--- a/public/templates/template_absensi.xlsx
+++ b/public/templates/template_absensi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\website\mirasa\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21373906-77E4-4FD7-9B1F-6C4E881F0744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685E9671-E0B0-477E-8DEF-2F47C805ECCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{48E1B71D-D519-48EA-AA0C-28489E471546}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{48E1B71D-D519-48EA-AA0C-28489E471546}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>tanggal</t>
   </si>
@@ -47,18 +47,6 @@
     <t>id_karyawan</t>
   </si>
   <si>
-    <t>nama_karyawan</t>
-  </si>
-  <si>
-    <t>devisi</t>
-  </si>
-  <si>
-    <t>kelompok</t>
-  </si>
-  <si>
-    <t>shift</t>
-  </si>
-  <si>
     <t>jam_masuk</t>
   </si>
   <si>
@@ -68,7 +56,31 @@
     <t>keterangan</t>
   </si>
   <si>
-    <t>nominal_gaji</t>
+    <t>MRSA-001</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>Hadir</t>
+  </si>
+  <si>
+    <t>kelompok_kerja_harian</t>
+  </si>
+  <si>
+    <t>status_kehadiran</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>LANGSUNG - IMF</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>15:00</t>
   </si>
 </sst>
 </file>
@@ -76,12 +88,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -96,12 +114,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -124,37 +142,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -489,257 +523,175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2967ED0-DADF-482D-A709-A6F8CF8E303D}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="8"/>
-    <col min="2" max="2" width="15.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="16" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="5" customWidth="1"/>
-    <col min="9" max="9" width="17" style="5" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="11" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="10"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="10"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="10"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="10"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="10"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="10"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="10"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="10"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="10"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="10"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="10"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="10"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1048576" xr:uid="{3D1D7538-7A6F-43A1-BF54-566807362E8E}">
-      <formula1>"Langsung, Tidak Langsung"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F1048576" xr:uid="{57459FA0-01FF-49C4-A842-EFF0DEABDB3F}">
-      <formula1>"Shift A, Shift B, Non Shift"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I1:I1048576" xr:uid="{0A751E91-D05D-45F7-9861-CE409DD6F95A}">
-      <formula1>"Hadir, Izin, Sakit"</formula1>
-    </dataValidation>
-  </dataValidations>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>